--- a/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_5505.xlsx
+++ b/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_5505.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1036,6 +1036,12 @@
           <t>5505-02-02-FG</t>
         </is>
       </c>
+      <c r="E12" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.33</v>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>5505-02-02-FG</t>
@@ -1048,12 +1054,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5505-02-02 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL1@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5505-02-02 (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5505-02-02 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5505-02-02 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | TAPDRILL1@BORE = Air-Way per-size tap drill -02 0.33 (A1) | TAPDRILL2@BORE = Air-Way per-size tap drill -02 0.33 (A1)</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1073,6 +1079,12 @@
           <t>5505-06-06-FG</t>
         </is>
       </c>
+      <c r="E13" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.57</v>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>5505-06-06-FG</t>
@@ -1085,12 +1097,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5505-06-06 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL1@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5505-06-06 (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5505-06-06 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5505-06-06 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | TAPDRILL1@BORE = Air-Way per-size tap drill -06 0.57 (A1) | TAPDRILL2@BORE = Air-Way per-size tap drill -06 0.57 (A1)</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1110,6 +1122,12 @@
           <t>5505-08-08-FG</t>
         </is>
       </c>
+      <c r="E14" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.7</v>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>5505-08-08-FG</t>
@@ -1122,12 +1140,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5505-08-08 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL1@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5505-08-08 (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5505-08-08 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5505-08-08 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | TAPDRILL1@BORE = Air-Way per-size tap drill -08 0.7 (A1) | TAPDRILL2@BORE = Air-Way per-size tap drill -08 0.7 (A1)</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1147,6 +1165,12 @@
           <t>5505-12-12-FG</t>
         </is>
       </c>
+      <c r="E15" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.91</v>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>5505-12-12-FG</t>
@@ -1159,12 +1183,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5505-12-12 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL1@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5505-12-12 (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5505-12-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5505-12-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | TAPDRILL1@BORE = Air-Way per-size tap drill -12 0.91 (A1) | TAPDRILL2@BORE = Air-Way per-size tap drill -12 0.91 (A1)</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1184,6 +1208,12 @@
           <t>5505-16-16-FG</t>
         </is>
       </c>
+      <c r="E16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.14</v>
+      </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>5505-16-16-FG</t>
@@ -1196,12 +1226,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5505-16-16 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL1@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5505-16-16 (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5505-16-16 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5505-16-16 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | TAPDRILL1@BORE = Air-Way per-size tap drill -16 1.14 (A1) | TAPDRILL2@BORE = Air-Way per-size tap drill -16 1.14 (A1)</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
